--- a/www/download/IND.compensation.empe_hs.r.pc.WIOD13.xlsx
+++ b/www/download/IND.compensation.empe_hs.r.pc.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>0.153864968584301</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>0.16029700854778</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.166954385727705</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>0.173855008300376</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>0.181019712145316</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>0.188472308501638</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>0.196239816083751</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>0.204603232753246</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>0.210571051646447</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>0.209717359901643</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209299821497889</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209299821497889</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209299821497889</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209299821497889</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>0.209299821497889</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>0.169044817094115</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>0.168630359599756</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>0.167903365965459</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>0.168023523377907</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.199963111373848</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>0.202676400790775</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>0.202802552594371</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>0.207401147367655</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>0.195924358814711</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>0.24918943413737</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>0.240157875391057</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>0.235950322844061</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>0.240306739208807</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.238106026799351</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>0.250441977970516</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>0.165843288808873</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>0.16971428572366</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>0.172865910570744</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>0.175109402495878</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>0.177047456686726</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>0.178402507200353</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0.179995020415257</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>0.180132552108903</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>0.166563098005101</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>0.191720799927915</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>0.195351821530963</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.198012537488662</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>0.203713298460781</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>0.223534403901085</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>0.225223664202211</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153249373821671</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>0.151591592079525</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>0.141357934736138</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>0.131085475404161</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>0.13503866866876</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>0.137628540907754</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>0.134641513454121</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>0.138774875738712</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0.123858063604186</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>0.171829178515103</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>0.181345393421768</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>0.184575841473869</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>0.19112187778463</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>0.207927195251845</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>0.211989600542139</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>0.28527207953238</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>0.289063672026907</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>0.292855264521435</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>0.296646857015962</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0.30043844951049</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>0.304230042005017</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>0.308021634499545</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>0.311813226994072</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>0.312940804118395</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>0.314068381242717</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>0.31519595836704</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>0.319739582810603</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>0.324283207254166</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>0.32882683169773</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>0.333370456141293</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0.165026836006221</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>0.174070473563283</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>0.18533569691959</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>0.191701460000232</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>0.19153353552202</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>0.196860559389073</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>0.205381127739414</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>0.208997566663107</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>0.211037923925837</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>0.216881218718759</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>0.222901783891316</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.233777121466238</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>0.240482936633715</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>0.235402302929652</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>0.248822892765799</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>0.0562093506386633</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>0.060132898282147</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>0.0642229342975888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>0.0684802104861104</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>0.0729051611681329</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>0.0774979069224905</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>0.082258260780203</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>0.0871857366777081</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>0.0972163267750453</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>0.102690348456082</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.11899884376754</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>0.134733325009745</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>0.131794604116846</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>0.140604669437637</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>0.140604669437637</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>0.390116927880701</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>0.384904366830866</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0.369970763777891</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>0.352881576519591</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>0.353397642917275</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>0.358280413431593</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>0.353910440875485</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>0.358248084348114</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>0.339631106733564</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>0.364859725162261</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347331262498627</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>0.353356172580841</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>0.36971202850082</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>0.361581828929178</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>0.361957673459242</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>0.166573778616233</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>0.166573778616233</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>0.166573778616233</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>0.166573778616233</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>0.169692810054207</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>0.174571254618226</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>0.180603645253425</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>0.183167233522844</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>0.164338498629227</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>0.196551407834206</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.199010445363947</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>0.204605442127207</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>0.204820376511823</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>0.207445680303656</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>0.22328919934111</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>0.292360206508077</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>0.294446300408508</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>0.296502004060942</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>0.309167344856546</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>0.300709474163641</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>0.302691879989424</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>0.307297726488227</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318450369437362</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>0.337570238433673</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>0.341056812054553</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0.339734656467144</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>0.338469540174099</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>0.337491902506053</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>0.347081543739561</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>0.36261815887713</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>0.223883473903054</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>0.23009214177032</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>0.236057132689494</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>0.245884667325644</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>0.250745961750358</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>0.255718720169047</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>0.263689990284609</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>0.268654797798724</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>0.299574972719611</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>0.302815111287093</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>0.313331495645102</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>0.318690099132054</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>0.289584372171691</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>0.310858210514823</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>0.312893410037268</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>0.27337934115787</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>0.293012019827709</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>0.299484675333469</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>0.316421547069308</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>0.325520561365048</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>0.344668661286352</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.356745111723183</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>0.366531484113573</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.33902574594464</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>0.377072787961434</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>0.389438216927018</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>0.392341691075884</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>0.393971012044968</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>0.392324552249411</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>0.406426619648174</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>0.432957307584914</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>0.424290485280814</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>0.414244980080208</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>0.401835231658574</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>0.391720262374542</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>0.396275348473721</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>0.391932582665419</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.39465875502121</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>0.358943598706702</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>0.396037207919124</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>0.41643028720111</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>0.409067485883032</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>0.38331425702095</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>0.372967861503811</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>0.389717279509351</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>0.318785191966435</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>0.325242969869431</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>0.328975048732311</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>0.33456523972237</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>0.345601204103223</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>34.74</t>
+          <t>0.347387444600473</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>0.348525926203091</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>0.353739437247561</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>0.341164951748857</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>0.37058464701845</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>0.374091954269727</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>0.379122833708382</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>0.396175341819239</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>0.403158238395283</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.420199510053656</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273592376994599</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>0.288068054217246</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>0.284083159498723</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>0.29461248402429</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>0.301886888327069</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>0.311240681765325</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>0.315466126812984</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>0.314644803851782</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>0.284851592450394</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>0.315755940723873</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>0.32678508147576</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>0.336017316639415</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>0.345621407234593</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>0.353555129748233</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>0.374934894575985</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>0.277767528904053</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>0.28488409319564</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>0.299234247700508</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>0.316493571632793</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>0.329116537176529</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>0.347523843868929</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>0.350137638080635</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.360656736409175</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>0.361891037278401</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>0.355932378530736</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>0.361792155573614</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>0.372400404706165</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>0.389528465053993</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>0.399501116619149</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>0.398407637829891</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>0.225340966083084</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>0.232948823909172</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>0.237226927667791</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>0.24118163639277</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>0.233904920813957</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>0.240836708288808</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>0.238602990085928</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>0.249243487413833</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.232599008054927</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>0.260788914447732</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>0.254222469856819</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.263245722347744</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>0.26784910933332</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>0.269016670729613</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>0.269727118190763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>0.248673669020027</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>0.248673669020027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>0.248673669020027</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>0.248673669020027</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>0.274666085932445</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>0.264220981115569</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0.260565849336195</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0.260562595586571</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.232534470264458</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.29407658987496</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>0.301025358744711</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>0.306541028936287</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>0.307605667431767</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>0.32737349179284</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>33.11</t>
+          <t>0.331122973069948</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>0.133862708237547</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>0.133862708237547</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>0.128514223825904</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>0.135152816633772</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>0.128149526003451</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>0.171006830839444</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>0.165549247462437</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>0.160804156557938</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>0.158431611105688</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15.61</t>
+          <t>0.156059065653439</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>0.207353637961907</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>0.233000924116142</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>0.228273588657747</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>0.228273588657747</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>0.228273588657747</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>0.215449898684455</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>0.215273192986451</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>0.215096487288446</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>0.214919781590441</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>0.214743075892436</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.235313607787725</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>0.255884139683014</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>0.276454671578303</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.297025203473592</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317595735368881</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317595735368881</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317595735368881</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317595735368881</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317595735368881</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317595735368881</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>0.228551949077892</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>0.243723137843603</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>0.249858280534478</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>0.263939145793767</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>0.276483269509155</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>0.28420368499428</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>0.292821454861932</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>0.310523354271164</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>0.331000979590364</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>0.348869083619875</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>0.365645356771562</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>0.409887125460397</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0.41008319108744</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>0.42418374560626</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>0.452934382739975</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115064863872481</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>0.122824041380863</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>0.131178552927775</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>0.139855419341338</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>0.151165718831045</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>0.158276403090031</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>0.148063865432393</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>0.148378488449053</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>0.138874929593949</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.141980402819401</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>0.150523193471181</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>0.155456241362467</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>15.72</t>
+          <t>0.157207962015697</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>0.176976462989848</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>0.171778646838757</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>0.230758021741052</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>0.238337633636048</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>0.241076805747217</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>0.251387734325517</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>0.256340884219462</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>0.260870477022473</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>0.271140539201546</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>0.285334184329508</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>0.286944809377974</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>0.290876712969125</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>0.292023635945964</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>0.292023635945964</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>0.292023635945964</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>0.292023635945964</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>0.292023635945964</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>0.331716691795572</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>0.354037887688592</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0.360021341046824</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>0.385882898215127</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>0.39689266710716</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>0.399947745631216</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.427682288313345</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>0.457678077948967</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.463015386857404</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>0.469383418714181</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0.490009375601123</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0.490009375601123</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0.490009375601123</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0.490009375601123</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0.490009375601123</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>0.38297454039357</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.374950919159893</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>0.365446441330267</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>0.354082269774032</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>0.344615980455163</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>0.346596133326365</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.34174830988491</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>0.345725669120357</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>0.342606166961938</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>0.366551899886692</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>0.379590543195016</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>0.382423371633458</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>0.383804148482609</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>0.391863244594682</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>0.401402104157042</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>0.215648484415565</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>0.199784726402223</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>0.194140374058004</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.207255524009581</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>0.219736006353015</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>0.239224936158196</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>0.24046809022498</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.239416943370824</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>0.146919122300035</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>0.295206030427211</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>0.313319246614321</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>0.281567115377296</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>0.309432957137098</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>0.300690257049695</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>0.379798213490054</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>0.337479986825909</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0.330003801342482</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>0.320238755438438</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>0.308911232579517</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>0.302417281122463</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>0.304864401943408</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>0.299503042270685</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>0.301891604431734</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>0.252825706415686</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>0.307042313712825</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>0.286994506473726</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>0.29601822873383</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>0.316971631715025</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>0.377103430037909</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>0.377178843101775</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>0.264232512848511</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0.260649567512397</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>0.257777212422185</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>0.258718874243415</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>0.258198343384027</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>0.25746974392098</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>0.2548872709022</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.254020938125548</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>0.252218997298688</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>0.250427366936407</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>0.244327147766521</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>0.23850747229835</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>0.236927439505582</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>0.234167026327657</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>0.234167026327657</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153249373821671</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>0.151591592079525</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>0.141357934736138</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>0.131085475404161</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>0.13503866866876</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>0.137628540907754</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>0.134641513454121</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>0.138774875738712</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0.123858063604186</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>0.171829178515103</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>0.181345393421768</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>0.184575841473869</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>0.19112187778463</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>0.207927195251845</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>0.211989600542139</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>0.20338329807979</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>0.217718735841253</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>0.246065370493181</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>0.239809308186684</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>0.274745773150394</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>0.258347640491807</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>0.250979014873388</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273633430420754</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>0.283491993756359</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>0.330140487056565</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>0.336217130235099</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>0.333748231790221</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>0.319093753171804</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>0.333741192387393</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>0.339627936389669</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197493838927671</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197493838927671</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197493838927671</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197493838927671</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197493838927671</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>0.197493838927671</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>0.214380705497248</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>0.230918530591076</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>0.232116469535008</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>0.277251635777324</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>0.288095700635141</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>0.295513218664395</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>0.304555318021329</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>0.299157843309884</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>0.319155072994049</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153249373821671</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>0.151591592079525</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>0.141357934736138</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>0.131085475404161</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>0.13503866866876</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>0.137628540907754</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>0.134641513454121</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>0.138774875738712</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0.123858063604186</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>0.171829178515103</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>0.181345393421768</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>0.184575841473869</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>0.19112187778463</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>0.207927195251845</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>0.211989600542139</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153249373821671</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>0.151591592079525</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>0.141357934736138</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>0.131085475404161</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>0.13503866866876</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>0.137628540907754</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>0.134641513454121</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>0.138774875738712</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0.123858063604186</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>0.171829178515103</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>0.181345393421768</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>0.184575841473869</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>0.19112187778463</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>0.207927195251845</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>0.211989600542139</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>0.182644137456708</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>0.182644137456708</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>0.182644137456708</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>0.182644137456708</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>0.186392000176828</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>0.190853502739363</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197418348447124</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>0.201371650735483</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>0.20590896260967</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>0.208463226741578</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0.213949348034136</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0.213949348034136</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0.213949348034136</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0.213949348034136</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>0.213949348034136</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>0.171483143334509</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>0.171483143334509</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>0.171483143334509</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>0.171483143334509</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>0.168935470315182</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>0.1738213275488</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>0.17480836933318</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>0.167515496055335</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>16.37</t>
+          <t>0.163708469360586</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>0.192073523559564</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>0.214433707344593</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>0.225375204233753</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>0.215318684569931</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>0.213480703104851</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>0.221841624622938</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>0.246865638342609</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>0.246865638342609</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>0.246865638342609</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>0.246865638342609</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>0.257023267552655</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>0.279413119243087</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>0.230621348589472</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>0.257362321072398</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>0.285823508591103</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>0.300466154223845</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>0.30899248679988</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>0.31293809402232</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>0.314209084368503</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>0.321657071696235</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>0.341631791924359</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>0.175632394391622</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>0.178519764421943</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>0.182521612994752</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>0.185480918571493</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>0.199769360570896</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>0.218077092896323</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>0.225195429041695</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>0.231065372362702</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>0.22077703781729</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>0.238035604533249</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>0.249053314488781</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>0.25943802992654</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>0.262575913097484</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>0.27981093651643</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>0.292918479894697</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>0.196159356914378</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>0.205099460499401</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>0.224319242464061</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213597988326195</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>0.229665835837909</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>0.236521133701938</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>0.24724104079533</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>0.258404667943629</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273574401952396</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>0.253277563370187</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>0.261089069051448</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>0.268122020559815</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>0.274206541122043</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>0.278352587450768</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>0.282763303894695</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>0.278661046608263</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>0.287068902069005</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>0.295280418344885</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>0.303300390719474</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>0.311133312462363</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>0.318783395141901</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>0.326254586924336</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>0.333550589078339</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>0.341414762121223</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349165485148323</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>0.354232247339983</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>0.372099401365079</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>0.366770912127975</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>0.380458193364835</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>0.412754001468868</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>0.316193820598937</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>0.315040474579303</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>0.314148865416901</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324167870372589</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>0.325728184531695</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>0.338735173747623</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>0.347724687054552</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>0.349000421584222</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>0.340986203952517</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>0.359613721853134</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>0.361083830034479</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>0.369212977323187</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>0.364127458318386</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.375007521109898</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>0.379223506756898</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.228898648427933</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>0.231919837016752</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>0.233019160662987</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.235284951021892</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>0.240991356161571</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>0.247797250380012</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.249827856813299</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.256671032957441</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0.249986894033455</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>0.274989880290778</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282125256882255</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.287263989153529</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>0.289429468407217</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.297021226523762</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>0.306401074424642</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.228898648427933</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>0.231919837016752</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>0.233019160662987</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.235284951021892</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>0.240991356161571</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>0.247797250380012</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.249827856813299</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.256671032957441</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0.249986894033455</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>0.274989880290778</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282125256882255</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.287263989153529</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>0.289429468407217</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.297021226523762</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>0.306401074424642</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>compensation.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
